--- a/DateBase/orders/Dang Nguyen48_2026-9-3.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-9-3.xlsx
@@ -521,6 +521,9 @@
       <c r="C11" t="str">
         <v>651_大丽花 奶油桃子_undefined_undefined_5stems</v>
       </c>
+      <c r="F11" t="str">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -579,7 +582,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01010151010102030100</v>
+        <v>010101510101020301010</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-9-3.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-9-3.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -525,9 +525,17 @@
         <v>10</v>
       </c>
     </row>
+    <row r="12">
+      <c r="C12" t="str">
+        <v>454_蓝星花_tweedia blue_undefined_1bunch</v>
+      </c>
+      <c r="F12" t="str">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L12"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -582,7 +590,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>010101510101020301010</v>
+        <v>01010151010102030101030</v>
       </c>
     </row>
   </sheetData>
